--- a/output/final/ingr/ingr distributors (status checked)/status_check_report.xlsx
+++ b/output/final/ingr/ingr distributors (status checked)/status_check_report.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status changes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Status changes'!$A$1:$H$64</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Status changes'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="33" customHeight="1">
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Gillco Products, Inc. (acquired by Azelis)</t>
+          <t>Brenntag Brasil</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>https://gillco.com</t>
+          <t>https://www.brenntag.com</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -2092,7 +2092,7 @@
       <c r="F39" s="9" t="inlineStr"/>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Gillco Ingredients (acquired by Azelis)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Brenntag SA' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
+    <row r="40" ht="33" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Palmer Holland, Inc.</t>
+          <t>Gillco Products, Inc. (acquired by Azelis)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>https://palmerholland.com</t>
+          <t>https://gillco.com</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2126,7 +2126,7 @@
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Palmer Holland' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Gillco Ingredients (acquired by Azelis)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="33" customHeight="1">
+    <row r="41" ht="24" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Barentz Brazil</t>
+          <t>Palmer Holland, Inc.</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>https://brasil.barentz.com</t>
+          <t>https://palmerholland.com</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2160,7 +2160,7 @@
       <c r="F41" s="9" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Tovani Benzaquen Ingredientes (acquired by Barentz)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Palmer Holland' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Barentz Brasil</t>
+          <t>Barentz International B.V.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Tovani Benzaquén Ingredientes (acquired by Barentz International)</t>
+          <t>Barentz BV</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>tovani.com.br</t>
+          <t>barentz.com</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -2237,7 +2237,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
+    <row r="44" ht="33" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Asha Ram &amp; Sons Pvt. Ltd.</t>
+          <t>Barentz Brazil</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>asharam.in</t>
+          <t>https://brasil.barentz.com</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2262,7 +2262,7 @@
       <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Asha Ram &amp; Sons Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Tovani Benzaquen Ingredientes (acquired by Barentz)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1">
+    <row r="45" ht="33" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Asha Ram &amp; Sons</t>
+          <t>Barentz Brasil</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>https://asharamandsons.com</t>
+          <t>barentz.com</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2296,7 +2296,7 @@
       <c r="F45" s="9" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Asha Ram &amp; Sons Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Tovani Benzaquen Ingredientes (acquired by Barentz)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
+    <row r="46" ht="33" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2313,12 +2313,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>IMCD India</t>
+          <t>Tovani Benzaquén Ingredientes (acquired by Barentz International)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>https://www.imcd.in</t>
+          <t>tovani.com.br</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'IMCD India Private Limited' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Tovani Benzaquen Ingredientes (acquired by Barentz)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>IMCD Group</t>
+          <t>Asha Ram &amp; Sons Pvt. Ltd.</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>imcdgroup.com</t>
+          <t>asharam.in</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2364,7 +2364,7 @@
       <c r="F47" s="9" t="inlineStr"/>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'IMCD N.V.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Asha Ram &amp; Sons Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Barentz BV</t>
+          <t>Asha Ram &amp; Sons</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>barentz.com</t>
+          <t>https://asharamandsons.com</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2398,7 +2398,7 @@
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Barentz International B.V.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Asha Ram &amp; Sons Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Brenntag SE</t>
+          <t>IMCD India</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>brenntag.com</t>
+          <t>https://www.imcd.in</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -2432,7 +2432,7 @@
       <c r="F49" s="9" t="inlineStr"/>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Brenntag Specialties' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'IMCD India Private Limited' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Azelis Group NV</t>
+          <t>IMCD Group</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>https://azelis.com</t>
+          <t>imcdgroup.com</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Azelis S.A.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'IMCD N.V.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="33" customHeight="1">
+    <row r="51" ht="24" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Protesa (Produtos Veterinarios e Alimenticios Ltda)</t>
+          <t>Brenntag SE</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>https://www.protesa.com.br</t>
+          <t>brenntag.com</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -2500,7 +2500,7 @@
       <c r="F51" s="9" t="inlineStr"/>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Protesa Distribuidora de Nutricionais Ltda.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Brenntag Specialties' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="33" customHeight="1">
+    <row r="52" ht="24" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2517,12 +2517,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Protesa</t>
+          <t>Azelis Group NV</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>protesa.com.br</t>
+          <t>https://azelis.com</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Protesa Distribuidora de Nutricionais Ltda.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Azelis S.A.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>IMCD Switzerland</t>
+          <t>Azelis</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>imcd.ch</t>
+          <t>azelis.com</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2568,7 +2568,7 @@
       <c r="F53" s="9" t="inlineStr"/>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'IMCD Switzerland AG' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Azelis S.A.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>IMCD South Africa</t>
+          <t>Protesa (Produtos Veterinarios e Alimenticios Ltda)</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>https://www.imcdsa.co.za</t>
+          <t>https://www.protesa.com.br</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'IMCD South Africa (Pty) Ltd. (acquired by IMCD Group)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Protesa Distribuidora de Nutricionais Ltda.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
+    <row r="55" ht="33" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Ingrizo</t>
+          <t>Protesa</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>ingrizo.com</t>
+          <t>protesa.com.br</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
@@ -2636,7 +2636,7 @@
       <c r="F55" s="9" t="inlineStr"/>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Ingrizo NV' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Protesa Distribuidora de Nutricionais Ltda.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>PT. Jerindo Sari Utama</t>
+          <t>IMCD Switzerland</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>jerindo.com</t>
+          <t>imcd.ch</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2670,7 +2670,7 @@
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'PT Jerindo Sari Utama' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'IMCD Switzerland AG' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Melkweg Holland BV (acquired by VanDrie Group)</t>
+          <t>IMCD South Africa</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>https://melkweg.com</t>
+          <t>https://www.imcdsa.co.za</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
@@ -2704,7 +2704,7 @@
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Melkweg Holland B.V. (acquired by VanDrie Group)' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'IMCD South Africa (Pty) Ltd. (acquired by IMCD Group)' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Extensores Lacteos, S.A. de C.V.</t>
+          <t>Intercontinental Speciality Milk Co.</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>https://exprolac.com</t>
+          <t>intercosm.com</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2738,7 +2738,7 @@
       <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Same company as 'Extensores Lacteos S.A. de C.V.' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Intercontinental Speciality Milk Co., Ltd.' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="33" customHeight="1">
+    <row r="59" ht="24" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>lactoferrin_verified_distributors</t>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Sihashakthi International Pvt. Ltd.</t>
+          <t>Ingrizo</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>sihashakthi.com</t>
+          <t>ingrizo.com</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
@@ -2772,7 +2772,7 @@
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Same company as 'Sihashakthi International Pvt Ltd' (same website and country, or same name and city) - listed once.</t>
+          <t>Same company as 'Ingrizo NV' (same website and country, or same name and city) - listed once.</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
@@ -2781,8 +2781,178 @@
         </is>
       </c>
     </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>lactoferrin_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>PT. Jerindo Sari Utama</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>jerindo.com</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'PT Jerindo Sari Utama' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="33" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>lactoferrin_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Melkweg Holland BV (acquired by VanDrie Group)</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>https://melkweg.com</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Melkweg Holland B.V. (acquired by VanDrie Group)' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="33" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>lactoferrin_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Extensores Lacteos, S.A. de C.V.</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>https://exprolac.com</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Extensores Lacteos S.A. de C.V.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="33" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>lactoferrin_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Sihashakthi International Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>sihashakthi.lk</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Same company as 'Sihashakthi International Pvt., Ltd.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="33" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>lactoferrin_verified_distributors</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Sihashakthi International Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>sihashakthi.com</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Same company as 'Sihashakthi International Pvt., Ltd.' (same website and country, or same name and city) - listed once.</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H59"/>
+  <autoFilter ref="A1:H64"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -2842,6 +3012,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
